--- a/out/目次.xlsx
+++ b/out/目次.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B6EBF81-C3DD-40D3-8AB0-9C608598D47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA2DBD0B-E72C-44A5-AE5D-5A588ADA471A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6130" yWindow="880" windowWidth="19040" windowHeight="12700" xr2:uid="{0AB80AAF-07D0-498F-A01E-F5CF88014B3D}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="23840" windowHeight="12700" xr2:uid="{7B6F9D99-933A-4B2A-B0A3-567DE79A583E}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -212,7 +212,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{3EC94DD8-CEA6-4678-8609-E097D11F7D4D}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{C7D38D72-8275-4489-BF1A-B87C7765CF1A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -543,7 +543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40A5697D-F882-4AB8-A320-3DE382636ECA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86E04C1-8484-469A-930A-B29FBE12CEB0}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/out/目次.xlsx
+++ b/out/目次.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitwork\CreateTableOfContentsExcelUsingSheetNames\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA2DBD0B-E72C-44A5-AE5D-5A588ADA471A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C700A1A1-0FE3-48CB-AC5E-C5BC305DD52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="23840" windowHeight="12700" xr2:uid="{7B6F9D99-933A-4B2A-B0A3-567DE79A583E}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="23840" windowHeight="12700" xr2:uid="{7D46C327-6833-4EDF-8FF5-23CDD58656EB}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="2" r:id="rId1"/>
@@ -212,7 +212,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{C7D38D72-8275-4489-BF1A-B87C7765CF1A}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{F5842899-4D5E-4DB1-91F7-612CA8CF32F1}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -543,7 +543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86E04C1-8484-469A-930A-B29FBE12CEB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0138D93E-7809-4357-8B97-520CC7A85F93}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
